--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -517,16 +517,16 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>319.7</v>
+        <v>315.9</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>311.81</v>
+        <v>312.17</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>282.15</v>
+        <v>282.36</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>64.31</v>
+        <v>63.59</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -535,7 +535,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="J2" s="1" t="b">
         <v>1</v>
@@ -545,7 +545,7 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=64.3)</t>
+          <t>RSI not pulled back (RSI=63.6)</t>
         </is>
       </c>
     </row>
@@ -561,16 +561,16 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>513.53</v>
+        <v>510.25</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>429.97</v>
+        <v>432.6</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>429.4</v>
+        <v>429.43</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>55.76</v>
+        <v>54.98</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>1</v>
@@ -579,7 +579,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="J3" s="1" t="b">
         <v>1</v>
@@ -589,7 +589,7 @@
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=55.8)</t>
+          <t>RSI not pulled back (RSI=55.0)</t>
         </is>
       </c>
     </row>
@@ -605,16 +605,16 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>346.59</v>
+        <v>338.34</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>349.78</v>
+        <v>349.18</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>334.32</v>
+        <v>334.56</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>37.77</v>
+        <v>43.04</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
@@ -623,7 +623,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>8.199999999999999</v>
+        <v>10.4</v>
       </c>
       <c r="J4" s="1" t="b">
         <v>0</v>
@@ -633,7 +633,7 @@
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-2.02)</t>
+          <t>SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-2.43)</t>
         </is>
       </c>
     </row>
@@ -649,16 +649,16 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>266.43</v>
+        <v>259.07</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>251.66</v>
+        <v>251.95</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>238.68</v>
+        <v>238.73</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>38.71</v>
+        <v>37.59</v>
       </c>
       <c r="G5" s="2" t="b">
         <v>1</v>
@@ -667,7 +667,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J5" s="2" t="b">
         <v>1</v>
@@ -689,16 +689,16 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>217.55</v>
+        <v>218.9</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>208.42</v>
+        <v>208.58</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>195.67</v>
+        <v>195.8</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>50</v>
+        <v>51.12</v>
       </c>
       <c r="G6" s="1" t="b">
         <v>1</v>
@@ -707,7 +707,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="J6" s="1" t="b">
         <v>1</v>
@@ -717,7 +717,7 @@
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=50.0); volume elevated on pullback (ratio=1.46)</t>
+          <t>RSI not pulled back (RSI=51.1); volume elevated on pullback (ratio=1.39)</t>
         </is>
       </c>
     </row>
@@ -733,16 +733,16 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>578.02</v>
+        <v>572.55</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>592.14</v>
+        <v>592.05</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>622</v>
+        <v>621.73</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>43.82</v>
+        <v>40.37</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>0</v>
@@ -751,7 +751,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>15.2</v>
+        <v>16</v>
       </c>
       <c r="J7" s="1" t="b">
         <v>0</v>
@@ -761,7 +761,7 @@
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; SMA50 flattening/falling (trend weakening); pullback too deep (15.2% off high); MACD below zero line (momentum turned negative, MACD=-8.34)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; SMA50 flattening/falling (trend weakening); pullback too deep (16.0% off high); MACD below zero line (momentum turned negative, MACD=-7.54)</t>
         </is>
       </c>
     </row>
@@ -777,16 +777,16 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>348.75</v>
+        <v>365.84</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>360.47</v>
+        <v>359.78</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>400.93</v>
+        <v>400.56</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>58.93</v>
+        <v>64.34</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>0</v>
@@ -795,17 +795,17 @@
         <v>1</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J8" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=58.9); SMA50 flattening/falling (trend weakening); pullback too deep (18.0% off high); MACD below zero line (momentum turned negative, MACD=-0.25)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=64.3); SMA50 flattening/falling (trend weakening)</t>
         </is>
       </c>
     </row>

--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -517,16 +517,16 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>315.9</v>
+        <v>325.19</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>312.17</v>
+        <v>312.76</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>282.36</v>
+        <v>282.63</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>63.59</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -535,7 +535,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>7</v>
+        <v>4.3</v>
       </c>
       <c r="J2" s="1" t="b">
         <v>1</v>
@@ -545,7 +545,7 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=63.6)</t>
+          <t>RSI not pulled back (RSI=75.4)</t>
         </is>
       </c>
     </row>
@@ -561,16 +561,16 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>510.25</v>
+        <v>500.14</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>432.6</v>
+        <v>435.22</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>429.43</v>
+        <v>429.38</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>54.98</v>
+        <v>55.92</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>1</v>
@@ -579,7 +579,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J3" s="1" t="b">
         <v>1</v>
@@ -589,7 +589,7 @@
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=55.0)</t>
+          <t>RSI not pulled back (RSI=55.9)</t>
         </is>
       </c>
     </row>
@@ -605,16 +605,16 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>338.34</v>
+        <v>335.44</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>349.18</v>
+        <v>348.92</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>334.56</v>
+        <v>334.81</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>43.04</v>
+        <v>40.32</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
@@ -623,7 +623,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>10.4</v>
+        <v>11.2</v>
       </c>
       <c r="J4" s="1" t="b">
         <v>0</v>
@@ -633,7 +633,7 @@
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-2.43)</t>
+          <t>SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-2.89)</t>
         </is>
       </c>
     </row>
@@ -649,16 +649,16 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>259.07</v>
+        <v>254.52</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>251.95</v>
+        <v>252.4</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>238.73</v>
+        <v>238.78</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>37.59</v>
+        <v>37.91</v>
       </c>
       <c r="G5" s="2" t="b">
         <v>1</v>
@@ -667,7 +667,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>10.4</v>
       </c>
       <c r="J5" s="2" t="b">
         <v>1</v>
@@ -689,16 +689,16 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>218.9</v>
+        <v>218.79</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>208.58</v>
+        <v>208.82</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>195.8</v>
+        <v>195.93</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>51.12</v>
+        <v>45.58</v>
       </c>
       <c r="G6" s="1" t="b">
         <v>1</v>
@@ -717,7 +717,7 @@
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=51.1); volume elevated on pullback (ratio=1.39)</t>
+          <t>RSI not pulled back (RSI=45.6); volume elevated on pullback (ratio=1.38)</t>
         </is>
       </c>
     </row>
@@ -733,25 +733,25 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>572.55</v>
+        <v>580.22</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>592.05</v>
+        <v>592.37</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>621.73</v>
+        <v>621.6</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>40.37</v>
+        <v>50.54</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>0</v>
       </c>
       <c r="H7" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>16</v>
+        <v>14.8</v>
       </c>
       <c r="J7" s="1" t="b">
         <v>0</v>
@@ -761,7 +761,7 @@
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; SMA50 flattening/falling (trend weakening); pullback too deep (16.0% off high); MACD below zero line (momentum turned negative, MACD=-7.54)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=50.5); SMA50 flattening/falling (trend weakening); volume elevated on pullback (ratio=1.14); MACD below zero line (momentum turned negative, MACD=-6.23)</t>
         </is>
       </c>
     </row>
@@ -777,16 +777,16 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>365.84</v>
+        <v>356.33</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>359.78</v>
+        <v>358.85</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>400.56</v>
+        <v>400.2</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>64.34</v>
+        <v>61.65</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>0</v>
@@ -795,7 +795,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>14</v>
+        <v>16.2</v>
       </c>
       <c r="J8" s="1" t="b">
         <v>1</v>
@@ -805,7 +805,7 @@
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=64.3); SMA50 flattening/falling (trend weakening)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=61.7); SMA50 flattening/falling (trend weakening); pullback too deep (16.2% off high)</t>
         </is>
       </c>
     </row>

--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -517,16 +517,16 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>325.19</v>
+        <v>326.2</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>312.76</v>
+        <v>313.4</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>282.63</v>
+        <v>282.9</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>75.40000000000001</v>
+        <v>74.26000000000001</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -535,7 +535,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="J2" s="1" t="b">
         <v>1</v>
@@ -545,7 +545,7 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=75.4)</t>
+          <t>RSI not pulled back (RSI=74.3)</t>
         </is>
       </c>
     </row>
@@ -561,16 +561,16 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>500.14</v>
+        <v>496.01</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>435.22</v>
+        <v>437.69</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>429.38</v>
+        <v>429.37</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>55.92</v>
+        <v>50.04</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>1</v>
@@ -579,7 +579,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="J3" s="1" t="b">
         <v>1</v>
@@ -589,7 +589,7 @@
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=55.9)</t>
+          <t>RSI not pulled back (RSI=50.0)</t>
         </is>
       </c>
     </row>
@@ -605,16 +605,16 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>335.44</v>
+        <v>338.32</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>348.92</v>
+        <v>348.75</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>334.81</v>
+        <v>335.11</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>40.32</v>
+        <v>40.59</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
@@ -623,7 +623,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>11.2</v>
+        <v>10.4</v>
       </c>
       <c r="J4" s="1" t="b">
         <v>0</v>
@@ -633,7 +633,7 @@
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-2.89)</t>
+          <t>SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-3.08)</t>
         </is>
       </c>
     </row>
@@ -649,16 +649,16 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>254.52</v>
+        <v>255.44</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>252.4</v>
+        <v>252.84</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>238.78</v>
+        <v>238.88</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>37.91</v>
+        <v>40.45</v>
       </c>
       <c r="G5" s="2" t="b">
         <v>1</v>
@@ -667,7 +667,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>10.4</v>
+        <v>10.1</v>
       </c>
       <c r="J5" s="2" t="b">
         <v>1</v>
@@ -689,16 +689,16 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>218.79</v>
+        <v>225.89</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>208.82</v>
+        <v>209.31</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>195.93</v>
+        <v>196.12</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>45.58</v>
+        <v>50.43</v>
       </c>
       <c r="G6" s="1" t="b">
         <v>1</v>
@@ -707,17 +707,17 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="J6" s="1" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=45.6); volume elevated on pullback (ratio=1.38)</t>
+          <t>RSI not pulled back (RSI=50.4); volume elevated on pullback (ratio=1.34)</t>
         </is>
       </c>
     </row>
@@ -733,25 +733,25 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>580.22</v>
+        <v>595.34</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>592.37</v>
+        <v>593</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>621.6</v>
+        <v>621.52</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>50.54</v>
+        <v>50.15</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>0</v>
       </c>
       <c r="H7" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>14.8</v>
+        <v>12.6</v>
       </c>
       <c r="J7" s="1" t="b">
         <v>0</v>
@@ -761,7 +761,7 @@
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=50.5); SMA50 flattening/falling (trend weakening); volume elevated on pullback (ratio=1.14); MACD below zero line (momentum turned negative, MACD=-6.23)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=50.2); SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-4.02)</t>
         </is>
       </c>
     </row>
@@ -777,16 +777,16 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>356.33</v>
+        <v>354.2</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>358.85</v>
+        <v>358.3</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>400.2</v>
+        <v>399.96</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>61.65</v>
+        <v>56.28</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>0</v>
@@ -795,7 +795,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>16.2</v>
+        <v>16.7</v>
       </c>
       <c r="J8" s="1" t="b">
         <v>1</v>
@@ -805,7 +805,7 @@
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=61.7); SMA50 flattening/falling (trend weakening); pullback too deep (16.2% off high)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=56.3); SMA50 flattening/falling (trend weakening); pullback too deep (16.7% off high)</t>
         </is>
       </c>
     </row>

--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -37,12 +37,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
         <bgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -58,10 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -517,16 +510,16 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>326.2</v>
+        <v>329.45</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>313.4</v>
+        <v>314.11</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>282.9</v>
+        <v>283.18</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>74.26000000000001</v>
+        <v>75.52</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -535,7 +528,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J2" s="1" t="b">
         <v>1</v>
@@ -545,7 +538,7 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=74.3)</t>
+          <t>RSI not pulled back (RSI=75.5)</t>
         </is>
       </c>
     </row>
@@ -561,16 +554,16 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>496.01</v>
+        <v>511.08</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>437.69</v>
+        <v>440.63</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>429.37</v>
+        <v>429.4</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>50.04</v>
+        <v>59.82</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>1</v>
@@ -579,7 +572,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J3" s="1" t="b">
         <v>1</v>
@@ -589,7 +582,7 @@
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=50.0)</t>
+          <t>RSI not pulled back (RSI=59.8)</t>
         </is>
       </c>
     </row>
@@ -605,16 +598,16 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>338.32</v>
+        <v>341.87</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>348.75</v>
+        <v>348.66</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>335.11</v>
+        <v>335.44</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>40.59</v>
+        <v>45.6</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
@@ -623,7 +616,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>10.4</v>
+        <v>9.5</v>
       </c>
       <c r="J4" s="1" t="b">
         <v>0</v>
@@ -633,49 +626,53 @@
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-3.08)</t>
+          <t>RSI not pulled back (RSI=45.6); SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-2.95)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>255.44</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>252.84</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>238.88</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>40.45</v>
-      </c>
-      <c r="G5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="J5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="K5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>258.41</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>253.31</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>238.99</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>45.86</v>
+      </c>
+      <c r="G5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="J5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L5" s="1" t="inlineStr">
+        <is>
+          <t>RSI not pulled back (RSI=45.9)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -689,25 +686,25 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>225.89</v>
+        <v>227.56</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>209.31</v>
+        <v>209.86</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>196.12</v>
+        <v>196.3</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>50.43</v>
+        <v>51.71</v>
       </c>
       <c r="G6" s="1" t="b">
         <v>1</v>
       </c>
       <c r="H6" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="J6" s="1" t="b">
         <v>1</v>
@@ -717,7 +714,7 @@
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=50.4); volume elevated on pullback (ratio=1.34)</t>
+          <t>RSI not pulled back (RSI=51.7)</t>
         </is>
       </c>
     </row>
@@ -733,16 +730,16 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>595.34</v>
+        <v>614.37</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>593</v>
+        <v>594.09</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>621.52</v>
+        <v>621.54</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>50.15</v>
+        <v>58.84</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>0</v>
@@ -751,7 +748,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>12.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J7" s="1" t="b">
         <v>0</v>
@@ -761,7 +758,7 @@
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=50.2); SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-4.02)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=58.8); SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-0.77)</t>
         </is>
       </c>
     </row>
@@ -777,25 +774,25 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>354.2</v>
+        <v>382.43</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>358.3</v>
+        <v>358.49</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>399.96</v>
+        <v>399.86</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>56.28</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>0</v>
       </c>
       <c r="H8" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>16.7</v>
+        <v>10.1</v>
       </c>
       <c r="J8" s="1" t="b">
         <v>1</v>
@@ -805,7 +802,7 @@
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=56.3); SMA50 flattening/falling (trend weakening); pullback too deep (16.7% off high)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=64.8); SMA50 flattening/falling (trend weakening); volume elevated on pullback (ratio=1.16)</t>
         </is>
       </c>
     </row>

--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -510,16 +510,16 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>329.45</v>
+        <v>320.85</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>314.11</v>
+        <v>315.01</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>283.18</v>
+        <v>283.44</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>75.52</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -528,7 +528,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>3</v>
+        <v>5.6</v>
       </c>
       <c r="J2" s="1" t="b">
         <v>1</v>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=75.5)</t>
+          <t>RSI not pulled back (RSI=64.7)</t>
         </is>
       </c>
     </row>
@@ -554,16 +554,16 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>511.08</v>
+        <v>501.5</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>440.63</v>
+        <v>443.6</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>429.4</v>
+        <v>429.38</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>59.82</v>
+        <v>64.28</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>1</v>
@@ -572,7 +572,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J3" s="1" t="b">
         <v>1</v>
@@ -582,7 +582,7 @@
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=59.8)</t>
+          <t>RSI not pulled back (RSI=64.3)</t>
         </is>
       </c>
     </row>
@@ -598,16 +598,16 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>341.87</v>
+        <v>338.49</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>348.66</v>
+        <v>348.57</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>335.44</v>
+        <v>335.71</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>45.6</v>
+        <v>44.33</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
@@ -616,7 +616,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>9.5</v>
+        <v>10.4</v>
       </c>
       <c r="J4" s="1" t="b">
         <v>0</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=45.6); SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-2.95)</t>
+          <t>SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-2.98)</t>
         </is>
       </c>
     </row>
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>258.41</v>
+        <v>257.08</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>253.31</v>
+        <v>253.92</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>238.99</v>
+        <v>239.12</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>45.86</v>
+        <v>45.95</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="J5" s="1" t="b">
         <v>1</v>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>227.56</v>
+        <v>231.45</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>209.86</v>
+        <v>210.59</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>196.3</v>
+        <v>196.53</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>51.71</v>
+        <v>54.36</v>
       </c>
       <c r="G6" s="1" t="b">
         <v>1</v>
@@ -704,7 +704,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J6" s="1" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=51.7)</t>
+          <t>RSI not pulled back (RSI=54.4)</t>
         </is>
       </c>
     </row>
@@ -730,16 +730,16 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>614.37</v>
+        <v>611.83</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>594.09</v>
+        <v>595.39</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>621.54</v>
+        <v>621.58</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>58.84</v>
+        <v>68.59</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>0</v>
@@ -748,17 +748,17 @@
         <v>1</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>9.800000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="J7" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="1" t="b">
         <v>0</v>
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=58.8); SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-0.77)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=68.6); SMA50 flattening/falling (trend weakening)</t>
         </is>
       </c>
     </row>
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>382.43</v>
+        <v>352.06</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>358.49</v>
+        <v>357.91</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>399.86</v>
+        <v>399.55</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>64.81999999999999</v>
+        <v>54.23</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>0</v>
@@ -792,7 +792,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>10.1</v>
+        <v>17.2</v>
       </c>
       <c r="J8" s="1" t="b">
         <v>1</v>
@@ -802,7 +802,7 @@
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=64.8); SMA50 flattening/falling (trend weakening); volume elevated on pullback (ratio=1.16)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=54.2); SMA50 flattening/falling (trend weakening); volume elevated on pullback (ratio=1.29); pullback too deep (17.2% off high)</t>
         </is>
       </c>
     </row>

--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -510,16 +510,16 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>320.85</v>
+        <v>319.97</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>315.01</v>
+        <v>314.99</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>283.44</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>64.70999999999999</v>
+        <v>63.63</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -528,7 +528,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="J2" s="1" t="b">
         <v>1</v>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=64.7)</t>
+          <t>RSI not pulled back (RSI=63.6)</t>
         </is>
       </c>
     </row>
@@ -554,16 +554,16 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>501.5</v>
+        <v>499.7</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>443.6</v>
+        <v>443.56</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>429.38</v>
+        <v>429.37</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>64.28</v>
+        <v>62.82</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>1</v>
@@ -572,7 +572,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="J3" s="1" t="b">
         <v>1</v>
@@ -582,7 +582,7 @@
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=64.3)</t>
+          <t>RSI not pulled back (RSI=62.8)</t>
         </is>
       </c>
     </row>
@@ -598,25 +598,25 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>338.49</v>
+        <v>338.46</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>348.57</v>
+        <v>348.35</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>335.71</v>
+        <v>335.5</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>44.33</v>
+        <v>44.5</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
       </c>
       <c r="H4" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="J4" s="1" t="b">
         <v>0</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-2.98)</t>
+          <t>SMA50 flattening/falling (trend weakening); volume elevated on pullback (ratio=1.11); MACD below zero line (momentum turned negative, MACD=-2.96)</t>
         </is>
       </c>
     </row>
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>257.08</v>
+        <v>258.51</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>253.92</v>
+        <v>253.95</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>239.12</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>45.95</v>
+        <v>47.24</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="J5" s="1" t="b">
         <v>1</v>
@@ -670,7 +670,7 @@
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=45.9)</t>
+          <t>RSI not pulled back (RSI=47.2)</t>
         </is>
       </c>
     </row>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>231.45</v>
+        <v>230.36</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>210.59</v>
+        <v>210.57</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>196.53</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>54.36</v>
+        <v>53.68</v>
       </c>
       <c r="G6" s="1" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=54.4)</t>
+          <t>RSI not pulled back (RSI=53.7)</t>
         </is>
       </c>
     </row>
@@ -730,16 +730,16 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>611.83</v>
+        <v>616.77</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>595.39</v>
+        <v>595.49</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>621.58</v>
+        <v>621.61</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>68.59</v>
+        <v>69.88</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>0</v>
@@ -748,7 +748,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>10.2</v>
+        <v>9.5</v>
       </c>
       <c r="J7" s="1" t="b">
         <v>1</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=68.6); SMA50 flattening/falling (trend weakening)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=69.9); SMA50 flattening/falling (trend weakening)</t>
         </is>
       </c>
     </row>
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>352.06</v>
+        <v>354.08</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>357.91</v>
+        <v>357.95</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>399.55</v>
+        <v>399.56</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>54.23</v>
+        <v>54.97</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>0</v>
@@ -792,7 +792,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>17.2</v>
+        <v>16.7</v>
       </c>
       <c r="J8" s="1" t="b">
         <v>1</v>
@@ -802,7 +802,7 @@
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=54.2); SMA50 flattening/falling (trend weakening); volume elevated on pullback (ratio=1.29); pullback too deep (17.2% off high)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=55.0); SMA50 flattening/falling (trend weakening); volume elevated on pullback (ratio=1.37); pullback too deep (16.7% off high)</t>
         </is>
       </c>
     </row>

--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -510,16 +510,16 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>319.97</v>
+        <v>315.9</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>314.99</v>
+        <v>315.64</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>283.44</v>
+        <v>283.68</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>63.63</v>
+        <v>55.6</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -528,7 +528,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="J2" s="1" t="b">
         <v>1</v>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=63.6)</t>
+          <t>RSI not pulled back (RSI=55.6)</t>
         </is>
       </c>
     </row>
@@ -554,16 +554,16 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>499.7</v>
+        <v>491.45</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>443.56</v>
+        <v>445.95</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>429.37</v>
+        <v>429.38</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>62.82</v>
+        <v>56.24</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>1</v>
@@ -572,7 +572,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="J3" s="1" t="b">
         <v>1</v>
@@ -582,7 +582,7 @@
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=62.8)</t>
+          <t>RSI not pulled back (RSI=56.2)</t>
         </is>
       </c>
     </row>
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>338.46</v>
+        <v>338.6</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>348.35</v>
+        <v>348.38</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>335.5</v>
+        <v>335.77</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>44.5</v>
+        <v>44.43</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
       </c>
       <c r="H4" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
         <v>10.3</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>SMA50 flattening/falling (trend weakening); volume elevated on pullback (ratio=1.11); MACD below zero line (momentum turned negative, MACD=-2.96)</t>
+          <t>SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-2.96)</t>
         </is>
       </c>
     </row>
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>258.51</v>
+        <v>257.14</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>253.95</v>
+        <v>254.44</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>239.12</v>
+        <v>239.3</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>47.24</v>
+        <v>47.71</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="J5" s="1" t="b">
         <v>1</v>
@@ -670,7 +670,7 @@
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=47.2)</t>
+          <t>RSI not pulled back (RSI=47.7)</t>
         </is>
       </c>
     </row>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>230.36</v>
+        <v>225.65</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>210.57</v>
+        <v>211.23</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>196.53</v>
+        <v>196.75</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>53.68</v>
+        <v>54.1</v>
       </c>
       <c r="G6" s="1" t="b">
         <v>1</v>
@@ -704,7 +704,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" s="1" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=53.7)</t>
+          <t>RSI not pulled back (RSI=54.1)</t>
         </is>
       </c>
     </row>
@@ -730,16 +730,16 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>616.77</v>
+        <v>617.21</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>595.49</v>
+        <v>596.83</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>621.61</v>
+        <v>621.71</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>69.88</v>
+        <v>88.55</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>0</v>
@@ -748,7 +748,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="J7" s="1" t="b">
         <v>1</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=69.9); SMA50 flattening/falling (trend weakening)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=88.6); SMA50 flattening/falling (trend weakening)</t>
         </is>
       </c>
     </row>
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>354.08</v>
+        <v>368.22</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>357.95</v>
+        <v>357.72</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>399.56</v>
+        <v>399.39</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>54.97</v>
+        <v>59.77</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>0</v>
@@ -792,7 +792,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>16.7</v>
+        <v>13.4</v>
       </c>
       <c r="J8" s="1" t="b">
         <v>1</v>
@@ -802,7 +802,7 @@
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=55.0); SMA50 flattening/falling (trend weakening); volume elevated on pullback (ratio=1.37); pullback too deep (16.7% off high)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=59.8); SMA50 flattening/falling (trend weakening); volume elevated on pullback (ratio=1.21)</t>
         </is>
       </c>
     </row>

--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -510,16 +510,16 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>315.9</v>
+        <v>313.76</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>315.64</v>
+        <v>316.29</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>283.68</v>
+        <v>283.92</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>55.6</v>
+        <v>46.78</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -528,7 +528,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="J2" s="1" t="b">
         <v>1</v>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=55.6)</t>
+          <t>RSI not pulled back (RSI=46.8)</t>
         </is>
       </c>
     </row>
@@ -554,16 +554,16 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>491.45</v>
+        <v>493.36</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>445.95</v>
+        <v>448.51</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>429.38</v>
+        <v>429.44</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>56.24</v>
+        <v>56.12</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>1</v>
@@ -572,7 +572,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="J3" s="1" t="b">
         <v>1</v>
@@ -582,7 +582,7 @@
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=56.2)</t>
+          <t>RSI not pulled back (RSI=56.1)</t>
         </is>
       </c>
     </row>
@@ -598,16 +598,16 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>338.6</v>
+        <v>330.11</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>348.38</v>
+        <v>347.91</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>335.77</v>
+        <v>335.96</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>44.43</v>
+        <v>37.14</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
@@ -616,7 +616,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>10.3</v>
+        <v>12.5</v>
       </c>
       <c r="J4" s="1" t="b">
         <v>0</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-2.96)</t>
+          <t>price below SMA200; SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-3.62)</t>
         </is>
       </c>
     </row>
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>257.14</v>
+        <v>251.96</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>254.44</v>
+        <v>254.67</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>239.3</v>
+        <v>239.44</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>47.71</v>
+        <v>35.85</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>1</v>
@@ -660,17 +660,17 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>9.5</v>
+        <v>11.3</v>
       </c>
       <c r="J5" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=47.7)</t>
+          <t>MACD below zero line (momentum turned negative, MACD=-0.46)</t>
         </is>
       </c>
     </row>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>225.65</v>
+        <v>224.1</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>211.23</v>
+        <v>211.81</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>196.75</v>
+        <v>196.94</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>54.1</v>
+        <v>54.57</v>
       </c>
       <c r="G6" s="1" t="b">
         <v>1</v>
@@ -704,7 +704,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J6" s="1" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=54.1)</t>
+          <t>RSI not pulled back (RSI=54.6)</t>
         </is>
       </c>
     </row>
@@ -730,25 +730,25 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>617.21</v>
+        <v>650.51</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>596.83</v>
+        <v>598.51</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>621.71</v>
+        <v>622</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>88.55</v>
+        <v>89.31</v>
       </c>
       <c r="G7" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>9.4</v>
+        <v>4.5</v>
       </c>
       <c r="J7" s="1" t="b">
         <v>1</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=88.6); SMA50 flattening/falling (trend weakening)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=89.3); volume elevated on pullback (ratio=1.12)</t>
         </is>
       </c>
     </row>
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>368.22</v>
+        <v>369.1</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>357.72</v>
+        <v>356.86</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>399.39</v>
+        <v>399.22</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>59.77</v>
+        <v>56.11</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>0</v>
@@ -792,7 +792,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>13.4</v>
+        <v>13.2</v>
       </c>
       <c r="J8" s="1" t="b">
         <v>1</v>
@@ -802,7 +802,7 @@
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=59.8); SMA50 flattening/falling (trend weakening); volume elevated on pullback (ratio=1.21)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=56.1); SMA50 flattening/falling (trend weakening); volume elevated on pullback (ratio=1.20)</t>
         </is>
       </c>
     </row>

--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -510,16 +510,16 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>313.76</v>
+        <v>324.09</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>316.29</v>
+        <v>317.02</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>283.92</v>
+        <v>284.22</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>46.78</v>
+        <v>62.96</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -528,7 +528,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>7.7</v>
+        <v>4.6</v>
       </c>
       <c r="J2" s="1" t="b">
         <v>1</v>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=46.8)</t>
+          <t>RSI not pulled back (RSI=63.0)</t>
         </is>
       </c>
     </row>
@@ -554,16 +554,16 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>493.36</v>
+        <v>493.11</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>448.51</v>
+        <v>450.89</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>429.44</v>
+        <v>429.52</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>56.12</v>
+        <v>57.26</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>1</v>
@@ -572,7 +572,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="J3" s="1" t="b">
         <v>1</v>
@@ -582,7 +582,7 @@
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=56.1)</t>
+          <t>RSI not pulled back (RSI=57.3)</t>
         </is>
       </c>
     </row>
@@ -598,16 +598,16 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>330.11</v>
+        <v>331.43</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>347.91</v>
+        <v>347.4</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>335.96</v>
+        <v>336.18</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>37.14</v>
+        <v>41.35</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
@@ -616,7 +616,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="J4" s="1" t="b">
         <v>0</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>price below SMA200; SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-3.62)</t>
+          <t>price below SMA200; SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-3.95)</t>
         </is>
       </c>
     </row>
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>251.96</v>
+        <v>252.78</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>254.67</v>
+        <v>254.97</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>239.44</v>
+        <v>239.62</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>35.85</v>
+        <v>41.53</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>11.3</v>
+        <v>11</v>
       </c>
       <c r="J5" s="1" t="b">
         <v>0</v>
@@ -670,7 +670,7 @@
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>MACD below zero line (momentum turned negative, MACD=-0.46)</t>
+          <t>MACD below zero line (momentum turned negative, MACD=-0.81)</t>
         </is>
       </c>
     </row>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>224.1</v>
+        <v>218.49</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>211.81</v>
+        <v>212.17</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>196.94</v>
+        <v>197.13</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>54.57</v>
+        <v>51.07</v>
       </c>
       <c r="G6" s="1" t="b">
         <v>1</v>
@@ -704,17 +704,17 @@
         <v>1</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>2.7</v>
+        <v>5.2</v>
       </c>
       <c r="J6" s="1" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=54.6)</t>
+          <t>RSI not pulled back (RSI=51.1)</t>
         </is>
       </c>
     </row>
@@ -730,16 +730,16 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>650.51</v>
+        <v>651.4</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>598.51</v>
+        <v>600.34</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>622</v>
+        <v>622.34</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>89.31</v>
+        <v>88.2</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>1</v>
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J7" s="1" t="b">
         <v>1</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=89.3); volume elevated on pullback (ratio=1.12)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=88.2); volume elevated on pullback (ratio=1.19)</t>
         </is>
       </c>
     </row>
@@ -774,16 +774,16 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>369.1</v>
+        <v>366.07</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>356.86</v>
+        <v>355.75</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>399.22</v>
+        <v>399.07</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>56.11</v>
+        <v>57.36</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>0</v>
@@ -792,7 +792,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="J8" s="1" t="b">
         <v>1</v>
@@ -802,7 +802,7 @@
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=56.1); SMA50 flattening/falling (trend weakening); volume elevated on pullback (ratio=1.20)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=57.4); SMA50 flattening/falling (trend weakening); volume elevated on pullback (ratio=1.17)</t>
         </is>
       </c>
     </row>

--- a/Output/screener_results.xlsx
+++ b/Output/screener_results.xlsx
@@ -510,25 +510,25 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>324.09</v>
+        <v>334.38</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>317.02</v>
+        <v>317.87</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>284.22</v>
+        <v>284.55</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>62.96</v>
+        <v>71.69</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
       </c>
       <c r="H2" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>4.6</v>
+        <v>1.6</v>
       </c>
       <c r="J2" s="1" t="b">
         <v>1</v>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=63.0)</t>
+          <t>RSI not pulled back (RSI=71.7); volume elevated on pullback (ratio=1.16)</t>
         </is>
       </c>
     </row>
@@ -554,16 +554,16 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>493.11</v>
+        <v>495.17</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>450.89</v>
+        <v>453.11</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>429.52</v>
+        <v>429.65</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>57.26</v>
+        <v>57.25</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>1</v>
@@ -572,7 +572,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="J3" s="1" t="b">
         <v>1</v>
@@ -582,7 +582,7 @@
       </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=57.3)</t>
+          <t>RSI not pulled back (RSI=57.2)</t>
         </is>
       </c>
     </row>
@@ -598,16 +598,16 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>331.43</v>
+        <v>340.54</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>347.4</v>
+        <v>347.02</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>336.18</v>
+        <v>336.39</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>41.35</v>
+        <v>46.45</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
@@ -616,7 +616,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>12.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J4" s="1" t="b">
         <v>0</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>price below SMA200; SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-3.95)</t>
+          <t>RSI not pulled back (RSI=46.4); SMA50 flattening/falling (trend weakening); MACD below zero line (momentum turned negative, MACD=-3.39)</t>
         </is>
       </c>
     </row>
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>252.78</v>
+        <v>255.74</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>254.97</v>
+        <v>255.23</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>239.62</v>
+        <v>239.79</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>41.53</v>
+        <v>46.84</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J5" s="1" t="b">
         <v>0</v>
@@ -670,7 +670,7 @@
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>MACD below zero line (momentum turned negative, MACD=-0.81)</t>
+          <t>RSI not pulled back (RSI=46.8); MACD below zero line (momentum turned negative, MACD=-0.92)</t>
         </is>
       </c>
     </row>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>218.49</v>
+        <v>219.15</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>212.17</v>
+        <v>212.37</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>197.13</v>
+        <v>197.11</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>51.07</v>
+        <v>53.12</v>
       </c>
       <c r="G6" s="1" t="b">
         <v>1</v>
@@ -704,7 +704,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="J6" s="1" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>RSI not pulled back (RSI=51.1)</t>
+          <t>RSI not pulled back (RSI=53.1)</t>
         </is>
       </c>
     </row>
@@ -730,16 +730,16 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>651.4</v>
+        <v>648.27</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>600.34</v>
+        <v>600.91</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>622.34</v>
+        <v>622.58</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>88.2</v>
+        <v>83.92</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>1</v>
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="J7" s="1" t="b">
         <v>1</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=88.2); volume elevated on pullback (ratio=1.19)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); RSI not pulled back (RSI=83.9); volume elevated on pullback (ratio=1.15)</t>
         </is>
       </c>
     </row>
@@ -774,25 +774,25 @@
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>366.07</v>
+        <v>365.42</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>355.75</v>
+        <v>354.5</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>399.07</v>
+        <v>398.93</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>57.36</v>
+        <v>50.99</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>0</v>
       </c>
       <c r="H8" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>13.9</v>
+        <v>14.1</v>
       </c>
       <c r="J8" s="1" t="b">
         <v>1</v>
@@ -802,7 +802,7 @@
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=57.4); SMA50 flattening/falling (trend weakening); volume elevated on pullback (ratio=1.17)</t>
+          <t>no golden cross (SMA50 &lt;= SMA200); price below SMA200; RSI not pulled back (RSI=51.0); SMA50 flattening/falling (trend weakening)</t>
         </is>
       </c>
     </row>
